--- a/request_forms/028_resident_park_improvement_request_form--request_forms.xlsx
+++ b/request_forms/028_resident_park_improvement_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'park_maintenance',_'label':_'park_maintenance'}</t>
+          <t>park_maintenance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Park Maintenance', 'label': 'Park Maintenance'}</t>
+          <t>Park Maintenance</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'park_upgrade',_'label':_'park_upgrade'}</t>
+          <t>park_upgrade</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Park Upgrade', 'label': 'Park Upgrade'}</t>
+          <t>Park Upgrade</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'park_removal',_'label':_'park_removal'}</t>
+          <t>park_removal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Park Removal', 'label': 'Park Removal'}</t>
+          <t>Park Removal</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'bench',_'label':_'bench'}</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Bench', 'label': 'Bench'}</t>
+          <t>Bench</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'picnic_table',_'label':_'picnic_table'}</t>
+          <t>picnic_table</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Picnic Table', 'label': 'Picnic Table'}</t>
+          <t>Picnic Table</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'play_equipment',_'label':_'play_equipment'}</t>
+          <t>play_equipment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Play Equipment', 'label': 'Play Equipment'}</t>
+          <t>Play Equipment</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'frequently',_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Frequently', 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
